--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.22.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.22.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.22.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.22.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: registry, and sign the same â€œRegistered</t>
+          <t>L132: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: 34 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: said, a certificate whereof shall be duly registered, shall beâ€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]15</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]15</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L52: isolated marker/symbol line :: 15</t>
@@ -622,13 +626,13 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: :</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]15</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” --------A. D. eighteen, ------------------------------already regis-</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: of such deed or conveyance shall have been duly regis-•</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,26 +674,30 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 34 ã€‚</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: of such deed or conveyance shall have been duly regis-â€¢</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: of such deed or conveyance shall have been duly regis-•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
-      <c r="N3" s="1" t="inlineStr"/>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>L132: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | symbol-only separator/garbage line :: 34 。</t>
+        </is>
+      </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L104: symbol-only separator/garbage line :: 34.</t>
+          <t>L42: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
-      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>L86: punctuation artifact: double/multiple hyphen :: — --------A. D. eighteen, ------------------------------already regis-</t>
+        </is>
+      </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="1" t="inlineStr"/>
@@ -721,22 +729,14 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L141: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ame â€œRegistered this â€” day of</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: registry, and sign the same" Registered thisâ€” day of judgments</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: 7</t>
+          <t>L104: symbol-only separator/garbage line :: 34.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -773,15 +773,15 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” --------A. D. eighteen, ------------------------------already regis-</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L106: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
